--- a/section & items.xlsx
+++ b/section & items.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Free lance\Sara\New App - Sara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A12C762C-C64D-4FF7-B585-54A43074671B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3195C992-E6EF-440A-A20B-B9A84CCA4303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02FE0364-C0ED-4B2C-928D-39FF92506048}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{02FE0364-C0ED-4B2C-928D-39FF92506048}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="البنود" sheetId="1" r:id="rId1"/>
+    <sheet name="الاقسام" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="56">
   <si>
     <t>القسم</t>
   </si>
@@ -204,6 +205,9 @@
   </si>
   <si>
     <t>البند</t>
+  </si>
+  <si>
+    <t>أقسام المشاريع</t>
   </si>
 </sst>
 </file>
@@ -262,11 +266,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,6 +619,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261D6957-B89E-454D-B5B1-57BC50643FAF}">
   <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -613,435 +634,488 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A147ED28-9022-438B-AF41-04ED35F5F8DD}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" t="s">
-        <v>53</v>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
